--- a/booklets/User-story_spreadsheets.xlsx
+++ b/booklets/User-story_spreadsheets.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="8" count="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="9" count="9">
   <si>
     <t>Operator</t>
   </si>
@@ -34,6 +34,9 @@
   </si>
   <si>
     <t>environmental_sensor_cards.png</t>
+  </si>
+  <si>
+    <t>actuator_panel.png</t>
   </si>
   <si>
     <t>Developer</t>
@@ -549,7 +552,7 @@
         </is>
       </c>
       <c r="E13" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -579,7 +582,7 @@
         </is>
       </c>
       <c r="E14" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -594,7 +597,7 @@
         </is>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
@@ -607,7 +610,7 @@
         </is>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -637,7 +640,7 @@
         </is>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -667,7 +670,7 @@
         </is>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -682,7 +685,7 @@
         </is>
       </c>
       <c r="B18" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
@@ -695,7 +698,7 @@
         </is>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -723,7 +726,7 @@
         </is>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -753,7 +756,7 @@
         </is>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -783,7 +786,7 @@
         </is>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
